--- a/docs/export-templates/AI问书_XX出版社_主控台数据导出.xlsx
+++ b/docs/export-templates/AI问书_XX出版社_主控台数据导出.xlsx
@@ -4,15 +4,73 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="实时总览" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="经营分析" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="当前订阅" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="实时总览" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="经营分析" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="70">
+  <si>
+    <t>机构主控台 · 当前生效订阅（本机构）</t>
+  </si>
+  <si>
+    <t>导出时间：2026-07-14 10:00:00 · 实时统计时间：2026-07-14 10:00:00 · 本机构订阅与配额 · 不随机构筛选变化</t>
+  </si>
+  <si>
+    <t>筛选条件：经营分析区间＝近 7 天</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>配额项</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>统计口径</t>
+  </si>
+  <si>
+    <t>资源占用</t>
+  </si>
+  <si>
+    <t>KP 数</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>当前订阅上限 50 个。“当前占用”按机构真实内容实时统计并跨订阅延续；删除可释放。</t>
+  </si>
+  <si>
+    <t>存储</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>当前订阅上限 100 GB。“当前占用”按机构真实内容实时统计并跨订阅延续；删除可释放。</t>
+  </si>
+  <si>
+    <t>周期消耗</t>
+  </si>
+  <si>
+    <t>Token</t>
+  </si>
+  <si>
+    <t>亿</t>
+  </si>
+  <si>
+    <t>基础 2 亿 + 生效加油包 0.5 亿，当前上限 2.5 亿。“本周期消耗”绑定当前订阅周期且不可回收；新订阅生效时归零，旧额度不结转。</t>
+  </si>
   <si>
     <t>机构主控台 · 实时总览</t>
   </si>
@@ -20,24 +78,9 @@
     <t>导出时间：2026-07-14 10:00:00 · 实时统计时间：2026-07-14 10:00:00 · 截至导出时刻的实时快照，不参与环比</t>
   </si>
   <si>
-    <t>筛选条件：经营分析区间＝近 7 天</t>
-  </si>
-  <si>
-    <t>分类</t>
-  </si>
-  <si>
     <t>指标</t>
   </si>
   <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>统计口径</t>
-  </si>
-  <si>
     <t>经营</t>
   </si>
   <si>
@@ -92,43 +135,10 @@
     <t>按用户 ID 精确去重</t>
   </si>
   <si>
-    <t>资源占用</t>
-  </si>
-  <si>
-    <t>KP 数</t>
-  </si>
-  <si>
-    <t>个</t>
-  </si>
-  <si>
-    <t>当前订阅上限 50 个。“当前占用”按机构真实内容实时统计并跨订阅延续；删除可释放。</t>
-  </si>
-  <si>
-    <t>存储</t>
-  </si>
-  <si>
-    <t>GB</t>
-  </si>
-  <si>
-    <t>当前订阅上限 100 GB。“当前占用”按机构真实内容实时统计并跨订阅延续；删除可释放。</t>
-  </si>
-  <si>
-    <t>周期消耗</t>
-  </si>
-  <si>
-    <t>Token</t>
-  </si>
-  <si>
-    <t>亿</t>
-  </si>
-  <si>
-    <t>基础 2 亿 + 生效加油包 0.5 亿，当前上限 2.5 亿。“本周期消耗”绑定当前订阅周期且不可回收；新订阅生效时归零，旧额度不结转。</t>
-  </si>
-  <si>
     <t>机构主控台 · 经营分析</t>
   </si>
   <si>
-    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-09 ~ 2026-07-15） · 当前区间 07-09—07-15 · 对比 07-02—07-08</t>
+    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-31 ~ 2026-08-06） · 当前区间 07-31—08-06 · 对比 07-24—07-30</t>
   </si>
   <si>
     <t>数据类型</t>
@@ -152,7 +162,7 @@
     <t>↑ +3.5%</t>
   </si>
   <si>
-    <t>区间精确去重</t>
+    <t>区间内按用户 ID 去重</t>
   </si>
   <si>
     <t>新增会员</t>
@@ -161,13 +171,16 @@
     <t>↑ +8.8%</t>
   </si>
   <si>
+    <t>历史首次开通，按用户 ID 去重；续费/回流不计入</t>
+  </si>
+  <si>
     <t>区间 GMV</t>
   </si>
   <si>
     <t>↑ +5.6%</t>
   </si>
   <si>
-    <t>区间已支付</t>
+    <t>区间已支付（待支付/已失效不计入）</t>
   </si>
   <si>
     <t>区间提问数</t>
@@ -682,7 +695,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -744,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="6">
-        <v>86200</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>10</v>
@@ -761,132 +774,30 @@
         <v>12</v>
       </c>
       <c r="C6" s="9">
-        <v>1860</v>
+        <v>62</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.88</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="8" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="9">
-        <v>84340</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="6">
-        <v>860</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="9">
-        <v>12480</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="6">
-        <v>30</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="9">
-        <v>62</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.88</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -906,6 +817,179 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6">
+        <v>86200</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1860</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="9">
+        <v>84340</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6">
+        <v>860</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="9">
+        <v>12480</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E4"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -919,7 +1003,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -929,7 +1013,7 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -949,19 +1033,19 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>7</v>
@@ -969,362 +1053,362 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C5" s="6">
         <v>5364</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C6" s="9">
         <v>173</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C7" s="6">
         <v>11004</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C8" s="9">
         <v>8204</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9" s="6">
         <v>1157</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C10" s="9">
         <v>21</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11" s="6">
         <v>1088</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" s="9">
         <v>18</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C13" s="6">
         <v>1121</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C14" s="9">
         <v>20</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C15" s="6">
         <v>1236</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C16" s="9">
         <v>25</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C17" s="6">
         <v>1351</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C18" s="9">
         <v>30</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C19" s="6">
         <v>1384</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C20" s="9">
         <v>31</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C21" s="6">
         <v>1315</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C22" s="9">
         <v>28</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
